--- a/input/Studies/C3/C3_Prototypical_Sites/P6_3stages_gaslift.xlsx
+++ b/input/Studies/C3/C3_Prototypical_Sites/P6_3stages_gaslift.xlsx
@@ -13429,7 +13429,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -14948,7 +14947,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -15093,7 +15091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15409,6 +15407,16 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15593,6 +15601,12 @@
         <is>
           <t>gef_comp</t>
         </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15606,7 +15620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -15816,16 +15830,6 @@
     <row r="6">
       <c r="C6" s="4" t="n"/>
     </row>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
@@ -16276,7 +16280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:BD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16580,6 +16584,16 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16765,6 +16779,12 @@
           <t>VH_200_PS9_3stages</t>
         </is>
       </c>
+      <c r="BC2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16949,6 +16969,12 @@
         <is>
           <t>gef_comp</t>
         </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BD3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
